--- a/outputs/per-fund/vc-investments-maven11.xlsx
+++ b/outputs/per-fund/vc-investments-maven11.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Only Maven11. The full overview with all twenty funds is in vc-investments-full.xlsx.</t>
+          <t>Only Maven11. The full overview with all 59 funds is in vc-investments-full.xlsx.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>The twenty funds, with control totals per external source.</t>
+          <t>The 59 funds, with control totals per external source.</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>One row per company in which at least one of the twenty funds invested.</t>
+          <t>One row per company in which at least one of these 59 funds invested.</t>
         </is>
       </c>
     </row>
@@ -15172,11 +15172,11 @@
         <v>0</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, dragonfly, maven11, pantera</t>
+          <t>coinbase-ventures, dragonfly, fenbushi-capital, maven11, pantera</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
@@ -15235,11 +15235,11 @@
         <v>0</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, maven11</t>
+          <t>electric-capital, maven11, yzi-labs</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
@@ -15296,11 +15296,11 @@
         <v>0</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>borderless-capital, maven11</t>
         </is>
       </c>
       <c r="M4" s="7" t="inlineStr">
@@ -15359,11 +15359,11 @@
         <v>1</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, maven11</t>
+          <t>framework-ventures, maven11, parafi-capital</t>
         </is>
       </c>
       <c r="M5" s="7" t="inlineStr">
@@ -15481,11 +15481,11 @@
         <v>0</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>1kx, animoca-brands, coinfund, maven11</t>
         </is>
       </c>
       <c r="M7" s="10" t="n"/>
@@ -15542,11 +15542,11 @@
         <v>0</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>maven11, yzi-labs</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -15601,11 +15601,11 @@
         <v>0</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>lemniscap, maven11</t>
+          <t>alliance-dao, cms-holdings, hashkey-capital, lemniscap, maven11, mechanism-capital, okx-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
@@ -15664,11 +15664,11 @@
         <v>0</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>1kx, borderless-capital, cmt-digital, gsr, maven11, spartan-group</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
@@ -15723,11 +15723,11 @@
         <v>0</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, maven11</t>
+          <t>dragonfly, galaxy-digital, maven11, parafi-capital</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -15786,11 +15786,11 @@
         <v>2</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>alameda-research, blockchain-capital, cms-holdings, hypersphere, longhash-ventures, maven11, spartan-group</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
@@ -15849,11 +15849,11 @@
         <v>1</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>maven11, polychain</t>
+          <t>1kx, maven11, polychain</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -15912,11 +15912,11 @@
         <v>1</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>borderless-capital, fenbushi-capital, hypersphere, iosg-ventures, maven11</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
@@ -15971,11 +15971,11 @@
         <v>0</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, maven11</t>
+          <t>coinbase-ventures, maven11, spartan-group</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
@@ -16030,11 +16030,11 @@
         <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, maven11</t>
+          <t>framework-ventures, gsr, maven11</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
@@ -16211,11 +16211,11 @@
         <v>1</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, maven11</t>
+          <t>1kx, alliance-dao, blockchain-capital, digital-currency-group, electric-capital, gsr, maven11, spartan-group</t>
         </is>
       </c>
       <c r="M19" s="7" t="inlineStr">
@@ -16274,11 +16274,11 @@
         <v>0</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, maven11</t>
+          <t>framework-ventures, maven11, mechanism-capital, spartan-group</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -16337,11 +16337,11 @@
         <v>1</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, maven11, multicoin-capital</t>
+          <t>blockchain-capital, cmt-digital, framework-ventures, maven11, multicoin-capital</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
@@ -16400,11 +16400,11 @@
         <v>0</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>digital-currency-group, maven11, mechanism-capital, spartan-group</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -16463,11 +16463,11 @@
         <v>1</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>1kx, maven11</t>
         </is>
       </c>
       <c r="M23" s="7" t="inlineStr">
@@ -16711,11 +16711,11 @@
         <v>1</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, maven11</t>
+          <t>blockchain-capital, framework-ventures, maven11, parafi-capital</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -16774,11 +16774,11 @@
         <v>0</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>maven11, sevenx-ventures</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -16900,11 +16900,11 @@
         <v>2</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>alameda-research, maven11</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -16963,11 +16963,11 @@
         <v>0</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, maven11</t>
+          <t>animoca-brands, dragonfly, maven11</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -17026,11 +17026,11 @@
         <v>1</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>coinfund, galaxy-digital, hypersphere, maven11</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -17089,11 +17089,11 @@
         <v>0</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, maven11</t>
+          <t>figment-capital, gsr, hypersphere, longhash-ventures, maven11</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
@@ -17152,11 +17152,11 @@
         <v>1</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>maven11, spartan-group</t>
         </is>
       </c>
       <c r="M34" s="7" t="inlineStr">
@@ -17274,11 +17274,11 @@
         <v>0</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, lemniscap, maven11</t>
+          <t>blockchain-capital, coinbase-ventures, lemniscap, maven11, sevenx-ventures</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -17333,11 +17333,11 @@
         <v>2</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>alameda-research, blockchain-capital, coinfund, maven11, spartan-group</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
@@ -17398,11 +17398,11 @@
         <v>2</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, coinbase-ventures, delphi-ventures, figment-capital, maven11, polychain</t>
+          <t>bain-capital-crypto, blockchain-capital, coinbase-ventures, delphi-ventures, figment-capital, galaxy-digital, jump-crypto, maven11, mh-ventures, polychain, spartan-group</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
@@ -17526,11 +17526,11 @@
         <v>1</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>haun-ventures, maven11, robot-ventures</t>
+          <t>1kx, haun-ventures, maven11, robot-ventures</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
@@ -17589,11 +17589,11 @@
         <v>2</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>blockchain-capital, maven11</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
@@ -17652,11 +17652,11 @@
         <v>2</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>maven11, robot-ventures</t>
+          <t>galaxy-digital, maven11, robot-ventures</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
@@ -17715,11 +17715,11 @@
         <v>1</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, figment-capital, lemniscap, maven11, robot-ventures</t>
+          <t>1kx, delphi-ventures, figment-capital, lemniscap, maven11, robot-ventures</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -17778,11 +17778,11 @@
         <v>1</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>maven11, robot-ventures</t>
+          <t>circle-ventures, foresight-ventures, hashkey-capital, maven11, robot-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M44" s="7" t="inlineStr">
@@ -17904,11 +17904,11 @@
         <v>1</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>1kx, cmt-digital, maven11</t>
         </is>
       </c>
       <c r="M46" s="7" t="inlineStr">
@@ -18026,11 +18026,11 @@
         <v>1</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, maven11</t>
+          <t>a16z-crypto, coinfund, maven11</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr">
@@ -18085,11 +18085,11 @@
         <v>2</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>maven11, sfermion</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
@@ -18148,11 +18148,11 @@
         <v>1</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, delphi-ventures, figment-capital, maven11</t>
+          <t>bain-capital-crypto, blockchain-capital, delphi-ventures, fenbushi-capital, figment-capital, galaxy-digital, iosg-ventures, maven11</t>
         </is>
       </c>
       <c r="M50" s="7" t="inlineStr">
@@ -18211,11 +18211,11 @@
         <v>2</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, maven11</t>
+          <t>framework-ventures, maven11, spartan-group</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
@@ -18402,11 +18402,11 @@
         <v>1</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>1kx, maven11, mechanism-capital</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
@@ -18532,11 +18532,11 @@
         <v>1</v>
       </c>
       <c r="K56" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, maven11</t>
+          <t>figment-capital, iosg-ventures, maven11, sevenx-ventures</t>
         </is>
       </c>
       <c r="M56" s="7" t="inlineStr">
@@ -18595,11 +18595,11 @@
         <v>3</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>iosg-ventures, maven11, mirana-ventures</t>
         </is>
       </c>
       <c r="M57" s="7" t="inlineStr">
@@ -18658,11 +18658,11 @@
         <v>3</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, figment-capital, maven11</t>
+          <t>blockchain-capital, coinbase-ventures, digital-currency-group, figment-capital, maven11</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -18721,11 +18721,11 @@
         <v>1</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>borderless-capital, coinfund, maven11</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
@@ -18784,11 +18784,11 @@
         <v>1</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>maven11, polychain</t>
+          <t>circle-ventures, maven11, polychain</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -18847,11 +18847,11 @@
         <v>2</v>
       </c>
       <c r="K61" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, maven11, polychain</t>
+          <t>delphi-ventures, fenbushi-capital, hack-vc, maven11, polychain</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
@@ -18906,11 +18906,11 @@
         <v>1</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, dragonfly, maven11</t>
+          <t>delphi-ventures, dragonfly, maven11, okx-ventures</t>
         </is>
       </c>
       <c r="M62" s="7" t="inlineStr">
@@ -18969,11 +18969,11 @@
         <v>1</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>longhash-ventures, maven11</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
@@ -19028,11 +19028,11 @@
         <v>0</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>huobi-ventures, maven11, okx-ventures, sevenx-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
@@ -19091,11 +19091,11 @@
         <v>1</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>huobi-ventures, maven11, okx-ventures</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
@@ -19154,11 +19154,11 @@
         <v>1</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, maven11, polychain, robot-ventures</t>
+          <t>figment-capital, hack-vc, maven11, mh-ventures, okx-ventures, polychain, robot-ventures</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
@@ -19217,11 +19217,11 @@
         <v>1</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>founders-fund, maven11</t>
+          <t>1kx, cmt-digital, fenbushi-capital, founders-fund, maven11</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
@@ -19339,11 +19339,11 @@
         <v>2</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, maven11</t>
+          <t>figment-capital, galaxy-digital, maven11, sevenx-ventures</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
@@ -19402,11 +19402,11 @@
         <v>2</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>figment-capital, maven11</t>
+          <t>1kx, figment-capital, maven11</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
@@ -19465,11 +19465,11 @@
         <v>1</v>
       </c>
       <c r="K71" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>hypersphere, iosg-ventures, maven11</t>
         </is>
       </c>
       <c r="M71" s="7" t="inlineStr">
@@ -19583,11 +19583,11 @@
         <v>1</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>1kx, maven11</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
@@ -19646,11 +19646,11 @@
         <v>1</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>amber-group, big-brain-holdings, iosg-ventures, maven11, mirana-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
@@ -19772,11 +19772,11 @@
         <v>2</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>digital-currency-group, maven11</t>
         </is>
       </c>
       <c r="M76" s="7" t="inlineStr">
@@ -19835,11 +19835,11 @@
         <v>0</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>maven11, robot-ventures</t>
+          <t>big-brain-holdings, gsr, maven11, robot-ventures</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr">
@@ -19957,11 +19957,11 @@
         <v>1</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>founders-fund, maven11</t>
+          <t>founders-fund, maven11, mirana-ventures</t>
         </is>
       </c>
       <c r="M79" s="7" t="inlineStr">
@@ -20022,11 +20022,11 @@
         <v>1</v>
       </c>
       <c r="K80" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>maven11, robot-ventures</t>
+          <t>alliance-dao, maven11, robot-ventures</t>
         </is>
       </c>
       <c r="M80" s="7" t="inlineStr">
@@ -20085,11 +20085,11 @@
         <v>1</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>digital-currency-group, maven11</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
@@ -20148,11 +20148,11 @@
         <v>1</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>maven11, robot-ventures</t>
+          <t>alliance-dao, maven11, robot-ventures</t>
         </is>
       </c>
       <c r="M82" s="7" t="inlineStr">
@@ -20211,11 +20211,11 @@
         <v>1</v>
       </c>
       <c r="K83" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>maven11, polychain</t>
+          <t>amber-group, cmt-digital, maven11, polychain</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
@@ -20337,11 +20337,11 @@
         <v>2</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, cyber-fund, maven11, robot-ventures</t>
+          <t>arrington-capital, coinbase-ventures, cyber-fund, maven11, robot-ventures</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
@@ -20400,11 +20400,11 @@
         <v>1</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, maven11, robot-ventures</t>
+          <t>delphi-ventures, maven11, mechanism-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M86" s="7" t="inlineStr">
@@ -20465,11 +20465,11 @@
         <v>2</v>
       </c>
       <c r="K87" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>1kx, blockchain-capital, hypersphere, maven11, okx-ventures</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
@@ -20528,11 +20528,11 @@
         <v>1</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund, maven11</t>
+          <t>cyber-fund, digital-currency-group, maven11</t>
         </is>
       </c>
       <c r="M88" s="7" t="inlineStr">
@@ -20587,11 +20587,11 @@
         <v>1</v>
       </c>
       <c r="K89" s="6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, maven11, pantera</t>
+          <t>arrington-capital, big-brain-holdings, borderless-capital, electric-capital, galaxy-digital, gsr, maven11, pantera, parafi-capital</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
@@ -20650,11 +20650,11 @@
         <v>1</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>digital-currency-group, gsr, hashkey-capital, maven11</t>
         </is>
       </c>
       <c r="M90" s="7" t="inlineStr">
@@ -20902,11 +20902,11 @@
         <v>2</v>
       </c>
       <c r="K94" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>amber-group, cms-holdings, hashkey-capital, maven11</t>
         </is>
       </c>
       <c r="M94" s="7" t="inlineStr">
@@ -20965,11 +20965,11 @@
         <v>1</v>
       </c>
       <c r="K95" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>cms-holdings, cmt-digital, galaxy-digital, gsr, maven11, okx-ventures</t>
         </is>
       </c>
       <c r="M95" s="7" t="inlineStr">
@@ -21154,11 +21154,11 @@
         <v>3</v>
       </c>
       <c r="K98" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>big-brain-holdings, maven11</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr">
@@ -21280,11 +21280,11 @@
         <v>1</v>
       </c>
       <c r="K100" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund, maven11</t>
+          <t>cyber-fund, hashed, maven11</t>
         </is>
       </c>
       <c r="M100" s="7" t="inlineStr">
@@ -21343,11 +21343,11 @@
         <v>1</v>
       </c>
       <c r="K101" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>gsr, maven11</t>
         </is>
       </c>
       <c r="M101" s="7" t="inlineStr">
@@ -21465,11 +21465,11 @@
         <v>0</v>
       </c>
       <c r="K103" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>maven11, yzi-labs</t>
         </is>
       </c>
       <c r="M103" s="7" t="inlineStr">
@@ -21528,11 +21528,11 @@
         <v>0</v>
       </c>
       <c r="K104" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>digital-currency-group, maven11</t>
         </is>
       </c>
       <c r="M104" s="7" t="inlineStr">
@@ -21587,11 +21587,11 @@
         <v>5</v>
       </c>
       <c r="K105" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>maven11</t>
+          <t>hack-vc, maven11, spartan-group</t>
         </is>
       </c>
       <c r="M105" s="7" t="inlineStr">
@@ -26558,19 +26558,19 @@
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Fondspagina toont een vast maximum aantal regels; dit is een displaylimiet en geen portefeuilletotaal.</t>
+          <t>The fund page shows a fixed maximum number of rows; this is a display limit, not a portfolio total.</t>
         </is>
       </c>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>Pagina levert geen leesbare portefeuillelijst in statische HTML (client-side gerenderd). Niet geteld; geen schatting gemaakt.</t>
+          <t>Page delivers no readable portfolio list in static HTML (client-side rendered). Not counted; no estimate made.</t>
         </is>
       </c>
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>Geen telling verkregen; niet geschat.</t>
+          <t>No count obtained; not estimated.</t>
         </is>
       </c>
       <c r="K2" s="6" t="n">
@@ -26578,7 +26578,7 @@
       </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>`investments` is CryptoRanks eigen telling. De zichtbare portefeuillelijst toont zonder account maar tien regels; die lijst is niet gebruikt.</t>
+          <t>`investments` is CryptoRank's own count. The visible portfolio list shows only ten rows without an account; that list was not used.</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
